--- a/Results.xlsx
+++ b/Results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chale\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aquisexchangelimited-my.sharepoint.com/personal/chale_aquis_eu/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186DC0DC-C2B0-4CBF-BA62-4E1C6CD18B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{186DC0DC-C2B0-4CBF-BA62-4E1C6CD18B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5502ADF3-E459-42AC-A9E6-BEF1DE54A2F8}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="0" windowWidth="9640" windowHeight="11370" xr2:uid="{BB37E97E-B7BA-431A-91DF-AC950243D9C0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
   <si>
     <t>week</t>
   </si>
@@ -342,6 +342,30 @@
   </si>
   <si>
     <t>0.088567, 0.167731, 0.131357, 0.163034, 0.800372, 0.500019, 0.206649, 0.588480</t>
+  </si>
+  <si>
+    <t>0.669556, 0.734173</t>
+  </si>
+  <si>
+    <t>0.693612, 1.000000</t>
+  </si>
+  <si>
+    <t>0.376500, 0.525082, 0.442594</t>
+  </si>
+  <si>
+    <t>0.361985, 0.412010, 0.421437, 0.416700</t>
+  </si>
+  <si>
+    <t>1.000000, 1.000000, 0.990000, 0.990000</t>
+  </si>
+  <si>
+    <t>0.452930, 0.409333, 0.631830, 0.739800, 0.129381</t>
+  </si>
+  <si>
+    <t>0.165154, 0.250080, 0.549909, 0.253314, 0.284687, 0.676488</t>
+  </si>
+  <si>
+    <t>0.095001, 0.139292, 0.119306, 0.147069, 0.819451, 0.469514, 0.203887, 0.575004</t>
   </si>
 </sst>
 </file>
@@ -897,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60A3B5F3-BE9E-4D63-9D51-1E3AAF1ED347}">
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="68.81640625" bestFit="1" customWidth="1"/>
@@ -2089,6 +2113,97 @@
         <v>9.9991470161630005</v>
       </c>
     </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>13</v>
+      </c>
+      <c r="B110">
+        <v>1</v>
+      </c>
+      <c r="C110" t="s">
+        <v>101</v>
+      </c>
+      <c r="D110" s="20">
+        <v>7.8071825926949201E-11</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B111">
+        <v>2</v>
+      </c>
+      <c r="C111" t="s">
+        <v>102</v>
+      </c>
+      <c r="D111">
+        <v>0.63482818574643896</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B112">
+        <v>3</v>
+      </c>
+      <c r="C112" t="s">
+        <v>103</v>
+      </c>
+      <c r="D112">
+        <v>-1.2962526170438001E-2</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B113">
+        <v>4</v>
+      </c>
+      <c r="C113" t="s">
+        <v>104</v>
+      </c>
+      <c r="D113">
+        <v>0.73012179538908495</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B114">
+        <v>5</v>
+      </c>
+      <c r="C114" t="s">
+        <v>105</v>
+      </c>
+      <c r="D114">
+        <v>8284.8918411221803</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B115">
+        <v>6</v>
+      </c>
+      <c r="C115" t="s">
+        <v>106</v>
+      </c>
+      <c r="D115">
+        <v>-0.136426556148905</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B116">
+        <v>7</v>
+      </c>
+      <c r="C116" t="s">
+        <v>107</v>
+      </c>
+      <c r="D116">
+        <v>3.10131508483164</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B117">
+        <v>8</v>
+      </c>
+      <c r="C117" t="s">
+        <v>108</v>
+      </c>
+      <c r="D117">
+        <v>9.9982724186289005</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
